--- a/reports/orcid_report.xlsx
+++ b/reports/orcid_report.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25 July 2026 18:25:16</t>
+          <t>26 July 2026 01:20:28</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
